--- a/RapidCarbonation_OpenLCAModelResults.xlsx
+++ b/RapidCarbonation_OpenLCAModelResults.xlsx
@@ -5,26 +5,27 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anbarron\Box\Research\Projects\RCB\LCATEA\DataSharing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/2206556795696/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C917F2-7E66-43D9-B9D5-26798AA12070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{90C917F2-7E66-43D9-B9D5-26798AA12070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21B33383-645F-4945-91E6-4D09416E1025}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="8" xr2:uid="{74492F69-CD30-4A7D-8E48-49334AD3C91E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{74492F69-CD30-4A7D-8E48-49334AD3C91E}"/>
   </bookViews>
   <sheets>
-    <sheet name="TraditionalSize_Info" sheetId="1" r:id="rId1"/>
-    <sheet name="TraditionalSize_LCIA" sheetId="2" r:id="rId2"/>
-    <sheet name="BGALSize_Info" sheetId="3" r:id="rId3"/>
-    <sheet name="BGALSize_LCIA" sheetId="4" r:id="rId4"/>
-    <sheet name="TraditionalChiller_Info" sheetId="5" r:id="rId5"/>
-    <sheet name="TraditionalChiller_LCIA" sheetId="6" r:id="rId6"/>
-    <sheet name="BGALChiller_Info" sheetId="7" r:id="rId7"/>
-    <sheet name="BGALChiller_LCIA" sheetId="8" r:id="rId8"/>
-    <sheet name="TraditionalTime_Info" sheetId="9" r:id="rId9"/>
-    <sheet name="TraditionalTime_LCIA" sheetId="10" r:id="rId10"/>
-    <sheet name="BGALTime_Info" sheetId="11" r:id="rId11"/>
-    <sheet name="BGALTime_LCIA" sheetId="12" r:id="rId12"/>
+    <sheet name="README" sheetId="13" r:id="rId1"/>
+    <sheet name="TraditionalSize_Info" sheetId="1" r:id="rId2"/>
+    <sheet name="TraditionalSize_LCIA" sheetId="2" r:id="rId3"/>
+    <sheet name="BGALSize_Info" sheetId="3" r:id="rId4"/>
+    <sheet name="BGALSize_LCIA" sheetId="4" r:id="rId5"/>
+    <sheet name="TraditionalChiller_Info" sheetId="5" r:id="rId6"/>
+    <sheet name="TraditionalChiller_LCIA" sheetId="6" r:id="rId7"/>
+    <sheet name="BGALChiller_Info" sheetId="7" r:id="rId8"/>
+    <sheet name="BGALChiller_LCIA" sheetId="8" r:id="rId9"/>
+    <sheet name="TraditionalTime_Info" sheetId="9" r:id="rId10"/>
+    <sheet name="TraditionalTime_LCIA" sheetId="10" r:id="rId11"/>
+    <sheet name="BGALTime_Info" sheetId="11" r:id="rId12"/>
+    <sheet name="BGALTime_LCIA" sheetId="12" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="133">
   <si>
     <t>Project result</t>
   </si>
@@ -395,6 +396,90 @@
 During the carbonation step, the warm beer is pumped from the fermenter, through inline filters, through an inline chiller attached to the glycol supply, and sprayed into the bright tank. Immediately, the beer is transferred from the bright tank into kegs/bottles for long term storage. In this SA, the carbonation rate, or time it takes to run all of the beer through the system, is altered 
 Once all of the beer has been transferred to storage, the pressure on the bright tank is releived and the bright tank is opened for cleaning. 
 </t>
+  </si>
+  <si>
+    <t>Tab Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This file contains the impact assessments for the work contained in "Techno-economic analysis and life cycle assessment for the rapid carbonation of beer" </t>
+  </si>
+  <si>
+    <t>Each tab contains either the project information or the LCIA ouput from OpenLCA 2.4.0 on the relavent sensitivity analysis</t>
+  </si>
+  <si>
+    <t>TraditionalSize_Info</t>
+  </si>
+  <si>
+    <t>TraditionalSize_LCIA</t>
+  </si>
+  <si>
+    <t>BGALSize_Info</t>
+  </si>
+  <si>
+    <t>BGALSize_LCIA</t>
+  </si>
+  <si>
+    <t>TraditionalChiller_Info</t>
+  </si>
+  <si>
+    <t>TraditionalChiller_LCIA</t>
+  </si>
+  <si>
+    <t>BGALChiller_Info</t>
+  </si>
+  <si>
+    <t>BGALChiller_LCIA</t>
+  </si>
+  <si>
+    <t>TraditionalTime_Info</t>
+  </si>
+  <si>
+    <t>TraditionalTime_LCIA</t>
+  </si>
+  <si>
+    <t>BGALTime_Info</t>
+  </si>
+  <si>
+    <t>BGALTime_LCIA</t>
+  </si>
+  <si>
+    <t>project information for traditional system sensitivity analysis with varying beer residence time in bright tank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">project information for traditional system size-based sensitivity analysis </t>
+  </si>
+  <si>
+    <t>LCIA ouputs for traditional system size-based sensitivity analysis</t>
+  </si>
+  <si>
+    <t>project information for BGAL system size-based sensitivity analysis</t>
+  </si>
+  <si>
+    <t>LCIA ouputs for BGAL system size-based sensitivity analysis</t>
+  </si>
+  <si>
+    <t>project information for traditional system sensitivity analysis with varying chiller energy demand</t>
+  </si>
+  <si>
+    <t>LCIA outputs for traditional system sensitivity analysis with varying chiller energy demand</t>
+  </si>
+  <si>
+    <t>project information for BGAL system sensitivity analysis with varying chiller energy demand</t>
+  </si>
+  <si>
+    <t>LCIA outputs for BGAL system sensitivity analysis with varying chiller energy demand</t>
+  </si>
+  <si>
+    <t>LCIA output for traditional system sensitivity analysis with varying beer residence time in bright tank</t>
+  </si>
+  <si>
+    <t>project information for BGAL system sensitivity analysis with varying beer flow rate through BGAL carbonator</t>
+  </si>
+  <si>
+    <t>LCIA output for BGAL system sensitivity analysis with varying beer flow rate through BGAL carbonator</t>
   </si>
 </sst>
 </file>
@@ -775,503 +860,126 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA22CA0-455F-47E7-AC5C-801CF2B19BB9}">
-  <dimension ref="B2:G34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C86115A-192A-4866-ADCC-CBB45B0DB3D4}">
+  <dimension ref="B2:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="255" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="210" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>22</v>
+        <v>118</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17">
-        <v>1.7</v>
-      </c>
-      <c r="E17">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="F17">
-        <v>3.4</v>
-      </c>
-      <c r="G17">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18">
-        <v>1.17</v>
-      </c>
-      <c r="E18">
-        <v>0.23</v>
-      </c>
-      <c r="F18">
-        <v>2.35</v>
-      </c>
-      <c r="G18">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19">
-        <v>1.17</v>
-      </c>
-      <c r="E19">
-        <v>0.23</v>
-      </c>
-      <c r="F19">
-        <v>2.35</v>
-      </c>
-      <c r="G19">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20">
-        <v>1.17</v>
-      </c>
-      <c r="E20">
-        <v>0.23</v>
-      </c>
-      <c r="F20">
-        <v>2.35</v>
-      </c>
-      <c r="G20">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21">
-        <v>1.4</v>
-      </c>
-      <c r="E21">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="F21">
-        <v>2.8</v>
-      </c>
-      <c r="G21">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22">
-        <v>1.4</v>
-      </c>
-      <c r="E22">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="F22">
-        <v>2.8</v>
-      </c>
-      <c r="G22">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23">
-        <v>1.4</v>
-      </c>
-      <c r="E23">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="F23">
-        <v>2.8</v>
-      </c>
-      <c r="G23">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24">
-        <v>1.4</v>
-      </c>
-      <c r="E24">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="F24">
-        <v>2.8</v>
-      </c>
-      <c r="G24">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25">
-        <v>1.4</v>
-      </c>
-      <c r="E25">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="F25">
-        <v>2.8</v>
-      </c>
-      <c r="G25">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26">
-        <v>247</v>
-      </c>
-      <c r="E26">
-        <v>247</v>
-      </c>
-      <c r="F26">
-        <v>247</v>
-      </c>
-      <c r="G26">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27">
-        <v>3.79</v>
-      </c>
-      <c r="E27">
-        <v>0.75</v>
-      </c>
-      <c r="F27">
-        <v>7.57</v>
-      </c>
-      <c r="G27">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28">
-        <v>3.66</v>
-      </c>
-      <c r="E28">
-        <v>0.72</v>
-      </c>
-      <c r="F28">
-        <v>7.32</v>
-      </c>
-      <c r="G28">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29">
-        <v>4.38</v>
-      </c>
-      <c r="E29">
-        <v>0.86</v>
-      </c>
-      <c r="F29">
-        <v>8.76</v>
-      </c>
-      <c r="G29">
-        <v>2.2799999999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30">
-        <v>4.32</v>
-      </c>
-      <c r="E30">
-        <v>0.85</v>
-      </c>
-      <c r="F30">
-        <v>8.64</v>
-      </c>
-      <c r="G30">
-        <v>2.16</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31">
-        <v>3.66</v>
-      </c>
-      <c r="E31">
-        <v>0.72</v>
-      </c>
-      <c r="F31">
-        <v>7.32</v>
-      </c>
-      <c r="G31">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32">
-        <v>0.06</v>
-      </c>
-      <c r="E32">
-        <v>0.01</v>
-      </c>
-      <c r="F32">
-        <v>0.13</v>
-      </c>
-      <c r="G32">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" t="s">
-        <v>29</v>
-      </c>
-      <c r="D33">
-        <v>1.7</v>
-      </c>
-      <c r="E33">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="F33">
-        <v>3.4</v>
-      </c>
-      <c r="G33">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34">
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="E34">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="F34">
-        <v>6.4000000000000001E-2</v>
-      </c>
-      <c r="G34">
-        <v>1.6E-2</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1280,6 +988,513 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8F8B7EB-8035-43EF-84B7-573C167F7233}">
+  <dimension ref="B2:G34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="195" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="E17">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="F17">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="G17">
+        <v>0.33500000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18">
+        <v>0.23</v>
+      </c>
+      <c r="E18">
+        <v>0.23</v>
+      </c>
+      <c r="F18">
+        <v>0.23</v>
+      </c>
+      <c r="G18">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19">
+        <v>0.23</v>
+      </c>
+      <c r="E19">
+        <v>0.23</v>
+      </c>
+      <c r="F19">
+        <v>0.23</v>
+      </c>
+      <c r="G19">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20">
+        <v>0.23</v>
+      </c>
+      <c r="E20">
+        <v>0.23</v>
+      </c>
+      <c r="F20">
+        <v>0.23</v>
+      </c>
+      <c r="G20">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E21">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F21">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G21">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E22">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F22">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G22">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E23">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F23">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G23">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E24">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F24">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G24">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E25">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F25">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G25">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26">
+        <v>494</v>
+      </c>
+      <c r="E26">
+        <v>987</v>
+      </c>
+      <c r="F26">
+        <v>123</v>
+      </c>
+      <c r="G26">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27">
+        <v>0.75</v>
+      </c>
+      <c r="E27">
+        <v>0.75</v>
+      </c>
+      <c r="F27">
+        <v>0.75</v>
+      </c>
+      <c r="G27">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28">
+        <v>0.72</v>
+      </c>
+      <c r="E28">
+        <v>0.72</v>
+      </c>
+      <c r="F28">
+        <v>0.72</v>
+      </c>
+      <c r="G28">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29">
+        <v>0.86199999999999999</v>
+      </c>
+      <c r="E29">
+        <v>0.86199999999999999</v>
+      </c>
+      <c r="F29">
+        <v>0.86199999999999999</v>
+      </c>
+      <c r="G29">
+        <v>0.86199999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30">
+        <v>0.84799999999999998</v>
+      </c>
+      <c r="E30">
+        <v>0.84799999999999998</v>
+      </c>
+      <c r="F30">
+        <v>0.84799999999999998</v>
+      </c>
+      <c r="G30">
+        <v>0.84799999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31">
+        <v>0.72</v>
+      </c>
+      <c r="E31">
+        <v>0.72</v>
+      </c>
+      <c r="F31">
+        <v>0.72</v>
+      </c>
+      <c r="G31">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E32">
+        <v>1.4E-2</v>
+      </c>
+      <c r="F32">
+        <v>1.4E-2</v>
+      </c>
+      <c r="G32">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="E33">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="F33">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="G33">
+        <v>0.33500000000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="E34">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="F34">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="G34">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EAB6F85-BD8C-4B25-B35C-30E03A1183AE}">
   <dimension ref="B2:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1532,7 +1747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FC8D139-EC29-4537-A72F-004D8BFB9B8D}">
   <dimension ref="B2:G28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1917,7 +2132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{168C7A4A-F089-4730-AB3C-BD86CAE2C16F}">
   <dimension ref="B2:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2171,6 +2386,511 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA22CA0-455F-47E7-AC5C-801CF2B19BB9}">
+  <dimension ref="B2:G34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="210" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17">
+        <v>1.7</v>
+      </c>
+      <c r="E17">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="F17">
+        <v>3.4</v>
+      </c>
+      <c r="G17">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18">
+        <v>1.17</v>
+      </c>
+      <c r="E18">
+        <v>0.23</v>
+      </c>
+      <c r="F18">
+        <v>2.35</v>
+      </c>
+      <c r="G18">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19">
+        <v>1.17</v>
+      </c>
+      <c r="E19">
+        <v>0.23</v>
+      </c>
+      <c r="F19">
+        <v>2.35</v>
+      </c>
+      <c r="G19">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20">
+        <v>1.17</v>
+      </c>
+      <c r="E20">
+        <v>0.23</v>
+      </c>
+      <c r="F20">
+        <v>2.35</v>
+      </c>
+      <c r="G20">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21">
+        <v>1.4</v>
+      </c>
+      <c r="E21">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F21">
+        <v>2.8</v>
+      </c>
+      <c r="G21">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22">
+        <v>1.4</v>
+      </c>
+      <c r="E22">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F22">
+        <v>2.8</v>
+      </c>
+      <c r="G22">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23">
+        <v>1.4</v>
+      </c>
+      <c r="E23">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F23">
+        <v>2.8</v>
+      </c>
+      <c r="G23">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24">
+        <v>1.4</v>
+      </c>
+      <c r="E24">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F24">
+        <v>2.8</v>
+      </c>
+      <c r="G24">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25">
+        <v>1.4</v>
+      </c>
+      <c r="E25">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F25">
+        <v>2.8</v>
+      </c>
+      <c r="G25">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26">
+        <v>247</v>
+      </c>
+      <c r="E26">
+        <v>247</v>
+      </c>
+      <c r="F26">
+        <v>247</v>
+      </c>
+      <c r="G26">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27">
+        <v>3.79</v>
+      </c>
+      <c r="E27">
+        <v>0.75</v>
+      </c>
+      <c r="F27">
+        <v>7.57</v>
+      </c>
+      <c r="G27">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28">
+        <v>3.66</v>
+      </c>
+      <c r="E28">
+        <v>0.72</v>
+      </c>
+      <c r="F28">
+        <v>7.32</v>
+      </c>
+      <c r="G28">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29">
+        <v>4.38</v>
+      </c>
+      <c r="E29">
+        <v>0.86</v>
+      </c>
+      <c r="F29">
+        <v>8.76</v>
+      </c>
+      <c r="G29">
+        <v>2.2799999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30">
+        <v>4.32</v>
+      </c>
+      <c r="E30">
+        <v>0.85</v>
+      </c>
+      <c r="F30">
+        <v>8.64</v>
+      </c>
+      <c r="G30">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31">
+        <v>3.66</v>
+      </c>
+      <c r="E31">
+        <v>0.72</v>
+      </c>
+      <c r="F31">
+        <v>7.32</v>
+      </c>
+      <c r="G31">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32">
+        <v>0.06</v>
+      </c>
+      <c r="E32">
+        <v>0.01</v>
+      </c>
+      <c r="F32">
+        <v>0.13</v>
+      </c>
+      <c r="G32">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33">
+        <v>1.7</v>
+      </c>
+      <c r="E33">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="F33">
+        <v>3.4</v>
+      </c>
+      <c r="G33">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="E34">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="F34">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="G34">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9E470F-76BD-4FCD-BAD6-FC99A12F86AF}">
   <dimension ref="B2:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2423,7 +3143,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A23D2E6-D8DF-400F-BE5A-B468A8374858}">
   <dimension ref="B2:G28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2808,7 +3528,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7160B8FF-1B6D-4DEE-AEE8-6A64E5B68D13}">
   <dimension ref="B2:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3061,7 +3781,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCAA89BD-A471-4D82-9BBF-7756316BBE3F}">
   <dimension ref="B2:G34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3566,7 +4286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5525841A-FECE-479A-A93A-08BD64C06F75}">
   <dimension ref="B2:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3819,7 +4539,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB6CEE6-F612-4937-A7C7-46639456EF17}">
   <dimension ref="B2:G28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4204,7 +4924,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A17470C-97F4-42EB-BE8B-80052930FEA4}">
   <dimension ref="B2:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4455,511 +5175,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8F8B7EB-8035-43EF-84B7-573C167F7233}">
-  <dimension ref="B2:G34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="255" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="195" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="E17">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="F17">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="G17">
-        <v>0.33500000000000002</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18">
-        <v>0.23</v>
-      </c>
-      <c r="E18">
-        <v>0.23</v>
-      </c>
-      <c r="F18">
-        <v>0.23</v>
-      </c>
-      <c r="G18">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19">
-        <v>0.23</v>
-      </c>
-      <c r="E19">
-        <v>0.23</v>
-      </c>
-      <c r="F19">
-        <v>0.23</v>
-      </c>
-      <c r="G19">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20">
-        <v>0.23</v>
-      </c>
-      <c r="E20">
-        <v>0.23</v>
-      </c>
-      <c r="F20">
-        <v>0.23</v>
-      </c>
-      <c r="G20">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E21">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="F21">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="G21">
-        <v>0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E22">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="F22">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="G22">
-        <v>0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E23">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="F23">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="G23">
-        <v>0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E24">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="F24">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="G24">
-        <v>0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E25">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="F25">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="G25">
-        <v>0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26">
-        <v>494</v>
-      </c>
-      <c r="E26">
-        <v>987</v>
-      </c>
-      <c r="F26">
-        <v>123</v>
-      </c>
-      <c r="G26">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27">
-        <v>0.75</v>
-      </c>
-      <c r="E27">
-        <v>0.75</v>
-      </c>
-      <c r="F27">
-        <v>0.75</v>
-      </c>
-      <c r="G27">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28">
-        <v>0.72</v>
-      </c>
-      <c r="E28">
-        <v>0.72</v>
-      </c>
-      <c r="F28">
-        <v>0.72</v>
-      </c>
-      <c r="G28">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29">
-        <v>0.86199999999999999</v>
-      </c>
-      <c r="E29">
-        <v>0.86199999999999999</v>
-      </c>
-      <c r="F29">
-        <v>0.86199999999999999</v>
-      </c>
-      <c r="G29">
-        <v>0.86199999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30">
-        <v>0.84799999999999998</v>
-      </c>
-      <c r="E30">
-        <v>0.84799999999999998</v>
-      </c>
-      <c r="F30">
-        <v>0.84799999999999998</v>
-      </c>
-      <c r="G30">
-        <v>0.84799999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31">
-        <v>0.72</v>
-      </c>
-      <c r="E31">
-        <v>0.72</v>
-      </c>
-      <c r="F31">
-        <v>0.72</v>
-      </c>
-      <c r="G31">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32">
-        <v>1.4E-2</v>
-      </c>
-      <c r="E32">
-        <v>1.4E-2</v>
-      </c>
-      <c r="F32">
-        <v>1.4E-2</v>
-      </c>
-      <c r="G32">
-        <v>1.4E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" t="s">
-        <v>29</v>
-      </c>
-      <c r="D33">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="E33">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="F33">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="G33">
-        <v>0.33500000000000002</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="E34">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="F34">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="G34">
-        <v>6.0000000000000001E-3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>